--- a/outputs/регламент_реклама_CPC_CPM_полки_WB.xlsx
+++ b/outputs/регламент_реклама_CPC_CPM_полки_WB.xlsx
@@ -12,6 +12,8 @@
     <sheet name="Настройка полок CPC" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Ежедневный мониторинг" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Калькулятор ставки" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="СПП и реклама" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Чистка мусорного трафика" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +86,27 @@
       <color rgb="00C55A11"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007030A0"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007030A0"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -110,6 +131,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +214,26 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1190,4 +1241,308 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>СПП И РЕКЛАМА — КАК РЕКЛАМА ВЛИЯЕТ НА СПП И ПРОДАЖИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>СПП упал (пример: с 49,3% до 39,3%, −10 пп) → заказы резко падают. Итоговый СПП = базовый + дополнительный.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Что</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Суть</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Базовый СПП</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>WB крутит им продажи в категории: надо разогнать — поднял, надо снизить поток — опустил.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Доп. СПП (до +10 пп)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Зависит от рекламных расходов за 14 дней (аналог соинвеста Ozon). Больше тратишь на рекламу — больше доп. СПП.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>От чего зависит итоговый СПП</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1) решения WB по категории, 2) цена товара (ценовые пороги!), 3) FBO/FBS, 4) регион, 5) рекламные расходы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Ценовые пороги</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Огромные скачки: напр. до 1 700 ₽ СПП 12%, выше 1 700 ₽ — 33%. Цену надо ставить с учётом порога.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>FBO/FBS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Разница почти ушла (±1%), но WB периодически снова разводит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Регион</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Несколько пп разницы (Москва ≠ Питер), зависит от наличия товара в регионе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>КАК считается доп. СПП</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>WB берёт рекламные расходы относительно ВСЕГО оборота кабинета, НЕ ДРР рекламируемых товаров. Пример: ДРР в кабинете 6,2%, но от всего оборота ~2% → доп СПП ~1,5%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Применяется ко ВСЕМ товарам</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Доп. СПП от рекламы действует на весь кабинет, не только на рекламируемые SKU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>ВЫВОД для юнитки</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Рекламный бюджет ~10% от оборота — фактически ОБЯЗАТЕЛЬНАЯ часть юнитки. Без неё цены неконкурентны (нет доп СПП).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Задача рекламы (комплекс)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Эти 10% должны ОДНОВРЕМЕННО: 1) давать доп СПП, 2) приносить доп трафик/заказы, 3) двигать товар выше. Иначе сольёте прибыль на ДРР.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="98" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>ЧИСТКА МУСОРНОГО ТРАФИКА И ОПТИМИЗАЦИЯ ДРР (особенно в CPC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Мусорные запросы сливают бюджет. В CPC нельзя исключать фразы, в CPM — нельзя до 100 показов. Единственный рычаг в CPC-поиске — чистка SEO карточки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Действие</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Найти мусорную фразу, по которой показывают не тот товар (напр. продаём джинсы, показывают по «пиджак»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Понять, какое слово в карточке притянуло фразу (разобрать фразу по словам).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Искать это слово ВЕЗДЕ: заголовок, описание, КАЖДАЯ характеристика, основная категория, доп. категории (WB добавляет сам).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Убрать слово (где возможно без потери релевантных ключей).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Через время показы по мусору могут уйти (не всегда и не сразу).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Повторять по каждой мусорной фразе и каждому товару. Начинать с самых крупных по расходу фраз.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>ВАЖНО: в CPC чистка SEO — фактически ЕДИНСТВЕННЫЙ способ снижать ДРР (кроме снижения ставки).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>Даже идеально почистив SEO, часть мусора останется — убрать весь нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Инструменты (EVIRMA и т.п.): по фразе показывают, какие слова и где именно встречаются в карточке; обратный разрез «Слова в запросах» — по слову видно все фразы и вхождения. Ускоряет работу в разы.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>